--- a/ekspor-xlsx/sac/enso_oni_bulanan.xlsx
+++ b/ekspor-xlsx/sac/enso_oni_bulanan.xlsx
@@ -432,25 +432,25 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>tahun</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>bulan</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>periode</t>
+          <t>period</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -460,7 +460,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>fase</t>
+          <t>enso_phase</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10435,7 +10435,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10792,7 +10792,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11653,7 +11653,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11905,7 +11905,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -13081,7 +13081,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -13375,7 +13375,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13438,7 +13438,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13543,7 +13543,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13900,7 +13900,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14005,7 +14005,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14677,7 +14677,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14719,7 +14719,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15118,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15475,7 +15475,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15580,7 +15580,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15769,7 +15769,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>La Nina kuat</t>
+          <t>Strong La Nina</t>
         </is>
       </c>
     </row>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16189,7 +16189,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16420,7 +16420,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16504,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16651,7 +16651,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16672,7 +16672,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16693,7 +16693,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17029,7 +17029,7 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17239,7 +17239,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17386,7 +17386,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17470,7 +17470,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17491,7 +17491,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17680,7 +17680,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17701,7 +17701,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17722,7 +17722,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17743,7 +17743,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18016,7 +18016,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18226,7 +18226,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18520,7 +18520,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18919,7 +18919,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -19087,7 +19087,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -19108,7 +19108,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -19129,7 +19129,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>El Nino kuat</t>
+          <t>Strong El Nino</t>
         </is>
       </c>
     </row>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19276,7 +19276,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19465,7 +19465,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19507,7 +19507,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
